--- a/data.mn/public/datasets/population-by-sex-mongolia.xlsx
+++ b/data.mn/public/datasets/population-by-sex-mongolia.xlsx
@@ -1,13 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="English" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Монгол" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +18,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +35,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +43,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -434,19 +423,495 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>year</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Female</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Male</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1956</v>
+      </c>
+      <c r="B2" t="n">
+        <v>425190</v>
+      </c>
+      <c r="C2" t="n">
+        <v>420291</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1963</v>
+      </c>
+      <c r="B3" t="n">
+        <v>509129</v>
+      </c>
+      <c r="C3" t="n">
+        <v>508029</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1969</v>
+      </c>
+      <c r="B4" t="n">
+        <v>600236</v>
+      </c>
+      <c r="C4" t="n">
+        <v>597359</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1979</v>
+      </c>
+      <c r="B5" t="n">
+        <v>796138</v>
+      </c>
+      <c r="C5" t="n">
+        <v>798868</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1989</v>
+      </c>
+      <c r="B6" t="n">
+        <v>1023285</v>
+      </c>
+      <c r="C6" t="n">
+        <v>1020669</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>1990</v>
+      </c>
+      <c r="B7" t="n">
+        <v>1079819</v>
+      </c>
+      <c r="C7" t="n">
+        <v>1073647</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>1991</v>
+      </c>
+      <c r="B8" t="n">
+        <v>1091813</v>
+      </c>
+      <c r="C8" t="n">
+        <v>1085404</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>1992</v>
+      </c>
+      <c r="B9" t="n">
+        <v>1082367</v>
+      </c>
+      <c r="C9" t="n">
+        <v>1075995</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>1993</v>
+      </c>
+      <c r="B10" t="n">
+        <v>1089403</v>
+      </c>
+      <c r="C10" t="n">
+        <v>1082495</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>1994</v>
+      </c>
+      <c r="B11" t="n">
+        <v>1110095</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1096797</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>1995</v>
+      </c>
+      <c r="B12" t="n">
+        <v>1128628</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1114370</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>1996</v>
+      </c>
+      <c r="B13" t="n">
+        <v>1146168</v>
+      </c>
+      <c r="C13" t="n">
+        <v>1129848</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>1997</v>
+      </c>
+      <c r="B14" t="n">
+        <v>1161916</v>
+      </c>
+      <c r="C14" t="n">
+        <v>1145568</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>1998</v>
+      </c>
+      <c r="B15" t="n">
+        <v>1178468</v>
+      </c>
+      <c r="C15" t="n">
+        <v>1161666</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>1999</v>
+      </c>
+      <c r="B16" t="n">
+        <v>1195512</v>
+      </c>
+      <c r="C16" t="n">
+        <v>1177981</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>2000</v>
+      </c>
+      <c r="B17" t="n">
+        <v>1212861</v>
+      </c>
+      <c r="C17" t="n">
+        <v>1190244</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>2001</v>
+      </c>
+      <c r="B18" t="n">
+        <v>1227695</v>
+      </c>
+      <c r="C18" t="n">
+        <v>1204702</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>2002</v>
+      </c>
+      <c r="B19" t="n">
+        <v>1242422</v>
+      </c>
+      <c r="C19" t="n">
+        <v>1223235</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>2003</v>
+      </c>
+      <c r="B20" t="n">
+        <v>1257253</v>
+      </c>
+      <c r="C20" t="n">
+        <v>1237838</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>2004</v>
+      </c>
+      <c r="B21" t="n">
+        <v>1270681</v>
+      </c>
+      <c r="C21" t="n">
+        <v>1251052</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>2005</v>
+      </c>
+      <c r="B22" t="n">
+        <v>1285467</v>
+      </c>
+      <c r="C22" t="n">
+        <v>1265614</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>2006</v>
+      </c>
+      <c r="B23" t="n">
+        <v>1323601</v>
+      </c>
+      <c r="C23" t="n">
+        <v>1259653</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>2007</v>
+      </c>
+      <c r="B24" t="n">
+        <v>1343197</v>
+      </c>
+      <c r="C24" t="n">
+        <v>1277249</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>2008</v>
+      </c>
+      <c r="B25" t="n">
+        <v>1364650</v>
+      </c>
+      <c r="C25" t="n">
+        <v>1301305</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>2009</v>
+      </c>
+      <c r="B26" t="n">
+        <v>1388135</v>
+      </c>
+      <c r="C26" t="n">
+        <v>1328140</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>2010</v>
+      </c>
+      <c r="B27" t="n">
+        <v>1418887</v>
+      </c>
+      <c r="C27" t="n">
+        <v>1342081</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>2011</v>
+      </c>
+      <c r="B28" t="n">
+        <v>1446943</v>
+      </c>
+      <c r="C28" t="n">
+        <v>1364723</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>2012</v>
+      </c>
+      <c r="B29" t="n">
+        <v>1474291</v>
+      </c>
+      <c r="C29" t="n">
+        <v>1393453</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>2013</v>
+      </c>
+      <c r="B30" t="n">
+        <v>1504434</v>
+      </c>
+      <c r="C30" t="n">
+        <v>1425843</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>2014</v>
+      </c>
+      <c r="B31" t="n">
+        <v>1529494</v>
+      </c>
+      <c r="C31" t="n">
+        <v>1466455</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>2015</v>
+      </c>
+      <c r="B32" t="n">
+        <v>1554166</v>
+      </c>
+      <c r="C32" t="n">
+        <v>1503612</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>2016</v>
+      </c>
+      <c r="B33" t="n">
+        <v>1585952</v>
+      </c>
+      <c r="C33" t="n">
+        <v>1533983</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>2017</v>
+      </c>
+      <c r="B34" t="n">
+        <v>1615529</v>
+      </c>
+      <c r="C34" t="n">
+        <v>1562370</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>2018</v>
+      </c>
+      <c r="B35" t="n">
+        <v>1646631</v>
+      </c>
+      <c r="C35" t="n">
+        <v>1591848</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>2019</v>
+      </c>
+      <c r="B36" t="n">
+        <v>1677293</v>
+      </c>
+      <c r="C36" t="n">
+        <v>1619573</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>2020</v>
+      </c>
+      <c r="B37" t="n">
+        <v>1708563</v>
+      </c>
+      <c r="C37" t="n">
+        <v>1648979</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B38" t="n">
+        <v>1735881</v>
+      </c>
+      <c r="C38" t="n">
+        <v>1674058</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B39" t="n">
+        <v>1761400</v>
+      </c>
+      <c r="C39" t="n">
+        <v>1696148</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B40" t="n">
+        <v>1786466</v>
+      </c>
+      <c r="C40" t="n">
+        <v>1718275</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B41" t="n">
+        <v>1808475</v>
+      </c>
+      <c r="C41" t="n">
+        <v>1736360</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C41"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>он</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Эмэгтэй</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Эрэгтэй</t>
         </is>
       </c>
     </row>
